--- a/Pasta4 TERMINAR.xlsx
+++ b/Pasta4 TERMINAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno.GR-D-DL-13.000\Documents\GitHub\AnaRaquel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{091DA07D-14D4-44DA-806B-C267A5590AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8CC6693-B759-4F23-8DE9-2ECFE1732D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12735" yWindow="495" windowWidth="16155" windowHeight="13440" xr2:uid="{F2E485C0-DFA8-4F3B-9CF1-4C71E1BCA264}"/>
   </bookViews>
@@ -614,7 +614,7 @@
       <c r="C4" s="5">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="7">
@@ -631,7 +631,7 @@
       <c r="C5" s="5">
         <v>3</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E5" s="7">
@@ -648,7 +648,7 @@
       <c r="C6" s="5">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="7">
@@ -665,7 +665,7 @@
       <c r="C7" s="5">
         <v>3</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="7">
@@ -682,7 +682,7 @@
       <c r="C8" s="5">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="7">
@@ -699,7 +699,7 @@
       <c r="C9" s="5">
         <v>7</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="7">
@@ -716,7 +716,7 @@
       <c r="C10" s="5">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="7">
@@ -733,7 +733,7 @@
       <c r="C11" s="5">
         <v>4</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="7">
@@ -750,7 +750,7 @@
       <c r="C12" s="5">
         <v>6</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E12" s="7">
@@ -767,7 +767,7 @@
       <c r="C13" s="5">
         <v>6</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="7">
@@ -784,7 +784,7 @@
       <c r="C14" s="5">
         <v>3</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E14" s="7">
@@ -801,7 +801,7 @@
       <c r="C15" s="5">
         <v>8</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E15" s="7">
@@ -818,7 +818,7 @@
       <c r="C16" s="5">
         <v>6</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E16" s="7">
@@ -835,7 +835,7 @@
       <c r="C17" s="5">
         <v>2</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>33</v>
       </c>
       <c r="E17" s="7">
@@ -852,7 +852,7 @@
       <c r="C18" s="5">
         <v>3</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E18" s="7">
@@ -869,7 +869,7 @@
       <c r="C19" s="5">
         <v>4</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="7">
@@ -886,7 +886,7 @@
       <c r="C20" s="5">
         <v>9</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E20" s="7">
@@ -903,7 +903,7 @@
       <c r="C21" s="5">
         <v>1</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="7">
@@ -920,7 +920,7 @@
       <c r="C22" s="5">
         <v>8</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E22" s="7">
@@ -937,7 +937,7 @@
       <c r="C23" s="5">
         <v>5</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E23" s="7">
@@ -954,7 +954,7 @@
       <c r="C24" s="5">
         <v>7</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E24" s="7">

--- a/Pasta4 TERMINAR.xlsx
+++ b/Pasta4 TERMINAR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno.GR-D-DL-13.000\Documents\GitHub\AnaRaquel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8CC6693-B759-4F23-8DE9-2ECFE1732D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6C5E0B6-85C8-4EE7-997B-4505C42265C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12735" yWindow="495" windowWidth="16155" windowHeight="13440" xr2:uid="{F2E485C0-DFA8-4F3B-9CF1-4C71E1BCA264}"/>
+    <workbookView xWindow="14325" yWindow="315" windowWidth="14250" windowHeight="13440" activeTab="1" xr2:uid="{F2E485C0-DFA8-4F3B-9CF1-4C71E1BCA264}"/>
   </bookViews>
   <sheets>
     <sheet name="CADASTRO" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
   <si>
     <t>NOME DO ALUNO</t>
   </si>
@@ -614,10 +614,12 @@
       <c r="C4" s="5">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>33</v>
+      <c r="D4" s="5" t="str">
+        <f>VLOOKUP(C4,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Word-Básico</v>
       </c>
       <c r="E4" s="7">
+        <f>VLOOKUP(C4,TABELA!A$1:C$10,3,TRUE)</f>
         <v>180</v>
       </c>
     </row>
@@ -631,10 +633,12 @@
       <c r="C5" s="5">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>34</v>
+      <c r="D5" s="5" t="str">
+        <f>VLOOKUP(C5,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Word-Avançado</v>
       </c>
       <c r="E5" s="7">
+        <f>VLOOKUP(C5,TABELA!A$1:C$10,3,TRUE)</f>
         <v>270</v>
       </c>
     </row>
@@ -648,10 +652,12 @@
       <c r="C6" s="5">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>33</v>
+      <c r="D6" s="5" t="str">
+        <f>VLOOKUP(C6,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Word-Básico</v>
       </c>
       <c r="E6" s="7">
+        <f>VLOOKUP(C6,TABELA!A$1:C$10,3,TRUE)</f>
         <v>180</v>
       </c>
     </row>
@@ -665,10 +671,12 @@
       <c r="C7" s="5">
         <v>3</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>34</v>
+      <c r="D7" s="5" t="str">
+        <f>VLOOKUP(C7,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Word-Avançado</v>
       </c>
       <c r="E7" s="7">
+        <f>VLOOKUP(C7,TABELA!A$1:C$10,3,TRUE)</f>
         <v>270</v>
       </c>
     </row>
@@ -682,10 +690,12 @@
       <c r="C8" s="5">
         <v>1</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>32</v>
+      <c r="D8" s="5" t="str">
+        <f>VLOOKUP(C8,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Internet</v>
       </c>
       <c r="E8" s="7">
+        <f>VLOOKUP(C8,TABELA!A$1:C$10,3,TRUE)</f>
         <v>150</v>
       </c>
     </row>
@@ -699,10 +709,12 @@
       <c r="C9" s="5">
         <v>7</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>38</v>
+      <c r="D9" s="5" t="str">
+        <f>VLOOKUP(C9,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Power Point-Avançado</v>
       </c>
       <c r="E9" s="7">
+        <f>VLOOKUP(C9,TABELA!A$1:C$10,3,TRUE)</f>
         <v>170</v>
       </c>
     </row>
@@ -716,10 +728,12 @@
       <c r="C10" s="5">
         <v>1</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
+      <c r="D10" s="5" t="str">
+        <f>VLOOKUP(C10,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Internet</v>
       </c>
       <c r="E10" s="7">
+        <f>VLOOKUP(C10,TABELA!A$1:C$10,3,TRUE)</f>
         <v>150</v>
       </c>
     </row>
@@ -733,10 +747,12 @@
       <c r="C11" s="5">
         <v>4</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>35</v>
+      <c r="D11" s="5" t="str">
+        <f>VLOOKUP(C11,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Excel-Básico</v>
       </c>
       <c r="E11" s="7">
+        <f>VLOOKUP(C11,TABELA!A$1:C$10,3,TRUE)</f>
         <v>200</v>
       </c>
     </row>
@@ -750,10 +766,12 @@
       <c r="C12" s="5">
         <v>6</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>37</v>
+      <c r="D12" s="5" t="str">
+        <f>VLOOKUP(C12,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Power Point-Básico</v>
       </c>
       <c r="E12" s="7">
+        <f>VLOOKUP(C12,TABELA!A$1:C$10,3,TRUE)</f>
         <v>120</v>
       </c>
     </row>
@@ -767,10 +785,12 @@
       <c r="C13" s="5">
         <v>6</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>37</v>
+      <c r="D13" s="5" t="str">
+        <f>VLOOKUP(C13,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Power Point-Básico</v>
       </c>
       <c r="E13" s="7">
+        <f>VLOOKUP(C13,TABELA!A$1:C$10,3,TRUE)</f>
         <v>120</v>
       </c>
     </row>
@@ -784,10 +804,12 @@
       <c r="C14" s="5">
         <v>3</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>34</v>
+      <c r="D14" s="5" t="str">
+        <f>VLOOKUP(C14,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Word-Avançado</v>
       </c>
       <c r="E14" s="7">
+        <f>VLOOKUP(C14,TABELA!A$1:C$10,3,TRUE)</f>
         <v>270</v>
       </c>
     </row>
@@ -801,11 +823,13 @@
       <c r="C15" s="5">
         <v>8</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>39</v>
+      <c r="D15" s="5" t="str">
+        <f>VLOOKUP(C15,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Access</v>
       </c>
       <c r="E15" s="7">
-        <v>270</v>
+        <f>VLOOKUP(C15,TABELA!A$1:C$10,3,TRUE)</f>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -818,10 +842,12 @@
       <c r="C16" s="5">
         <v>6</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>37</v>
+      <c r="D16" s="5" t="str">
+        <f>VLOOKUP(C16,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Power Point-Básico</v>
       </c>
       <c r="E16" s="7">
+        <f>VLOOKUP(C16,TABELA!A$1:C$10,3,TRUE)</f>
         <v>120</v>
       </c>
     </row>
@@ -835,10 +861,12 @@
       <c r="C17" s="5">
         <v>2</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>33</v>
+      <c r="D17" s="5" t="str">
+        <f>VLOOKUP(C17,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Word-Básico</v>
       </c>
       <c r="E17" s="7">
+        <f>VLOOKUP(C17,TABELA!A$1:C$10,3,TRUE)</f>
         <v>180</v>
       </c>
     </row>
@@ -852,10 +880,12 @@
       <c r="C18" s="5">
         <v>3</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>34</v>
+      <c r="D18" s="5" t="str">
+        <f>VLOOKUP(C18,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Word-Avançado</v>
       </c>
       <c r="E18" s="7">
+        <f>VLOOKUP(C18,TABELA!A$1:C$10,3,TRUE)</f>
         <v>270</v>
       </c>
     </row>
@@ -869,10 +899,12 @@
       <c r="C19" s="5">
         <v>4</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>35</v>
+      <c r="D19" s="5" t="str">
+        <f>VLOOKUP(C19,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Excel-Básico</v>
       </c>
       <c r="E19" s="7">
+        <f>VLOOKUP(C19,TABELA!A$1:C$10,3,TRUE)</f>
         <v>200</v>
       </c>
     </row>
@@ -886,10 +918,12 @@
       <c r="C20" s="5">
         <v>9</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>40</v>
+      <c r="D20" s="5" t="str">
+        <f>VLOOKUP(C20,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Access com VBA</v>
       </c>
       <c r="E20" s="7">
+        <f>VLOOKUP(C20,TABELA!A$1:C$10,3,TRUE)</f>
         <v>320</v>
       </c>
     </row>
@@ -903,10 +937,12 @@
       <c r="C21" s="5">
         <v>1</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>32</v>
+      <c r="D21" s="5" t="str">
+        <f>VLOOKUP(C21,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Internet</v>
       </c>
       <c r="E21" s="7">
+        <f>VLOOKUP(C21,TABELA!A$1:C$10,3,TRUE)</f>
         <v>150</v>
       </c>
     </row>
@@ -920,11 +956,13 @@
       <c r="C22" s="5">
         <v>8</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>39</v>
+      <c r="D22" s="5" t="str">
+        <f>VLOOKUP(C22,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Access</v>
       </c>
       <c r="E22" s="7">
-        <v>270</v>
+        <f>VLOOKUP(C22,TABELA!A$1:C$10,3,TRUE)</f>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -937,10 +975,12 @@
       <c r="C23" s="5">
         <v>5</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>36</v>
+      <c r="D23" s="5" t="str">
+        <f>VLOOKUP(C23,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Excel-Avançado</v>
       </c>
       <c r="E23" s="7">
+        <f>VLOOKUP(C23,TABELA!A$1:C$10,3,TRUE)</f>
         <v>250</v>
       </c>
     </row>
@@ -954,10 +994,12 @@
       <c r="C24" s="5">
         <v>7</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>38</v>
+      <c r="D24" s="5" t="str">
+        <f>VLOOKUP(C24,TABELA!A$1:C$10,2,TRUE)</f>
+        <v>Power Point-Avançado</v>
       </c>
       <c r="E24" s="7">
+        <f>VLOOKUP(C24,TABELA!A$1:C$10,3,TRUE)</f>
         <v>170</v>
       </c>
     </row>
